--- a/artfynd/A 27397-2025 artfynd.xlsx
+++ b/artfynd/A 27397-2025 artfynd.xlsx
@@ -972,7 +972,7 @@
         <v>125940765</v>
       </c>
       <c r="B4" t="n">
-        <v>98248</v>
+        <v>98249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27397-2025 artfynd.xlsx
+++ b/artfynd/A 27397-2025 artfynd.xlsx
@@ -972,7 +972,7 @@
         <v>125940765</v>
       </c>
       <c r="B4" t="n">
-        <v>98249</v>
+        <v>98251</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27397-2025 artfynd.xlsx
+++ b/artfynd/A 27397-2025 artfynd.xlsx
@@ -972,7 +972,7 @@
         <v>125940765</v>
       </c>
       <c r="B4" t="n">
-        <v>98251</v>
+        <v>98255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27397-2025 artfynd.xlsx
+++ b/artfynd/A 27397-2025 artfynd.xlsx
@@ -972,7 +972,7 @@
         <v>125940765</v>
       </c>
       <c r="B4" t="n">
-        <v>98255</v>
+        <v>98256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27397-2025 artfynd.xlsx
+++ b/artfynd/A 27397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125940706</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>125941678</v>
       </c>
       <c r="B3" t="n">
-        <v>57648</v>
+        <v>57649</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>125940765</v>
       </c>
       <c r="B4" t="n">
-        <v>98256</v>
+        <v>98258</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>125941601</v>
       </c>
       <c r="B5" t="n">
-        <v>56843</v>
+        <v>56844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27397-2025 artfynd.xlsx
+++ b/artfynd/A 27397-2025 artfynd.xlsx
@@ -972,7 +972,7 @@
         <v>125940765</v>
       </c>
       <c r="B4" t="n">
-        <v>98258</v>
+        <v>98260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27397-2025 artfynd.xlsx
+++ b/artfynd/A 27397-2025 artfynd.xlsx
@@ -972,7 +972,7 @@
         <v>125940765</v>
       </c>
       <c r="B4" t="n">
-        <v>98260</v>
+        <v>98262</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27397-2025 artfynd.xlsx
+++ b/artfynd/A 27397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125940706</v>
       </c>
       <c r="B2" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>125941678</v>
       </c>
       <c r="B3" t="n">
-        <v>57649</v>
+        <v>57653</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>125940765</v>
       </c>
       <c r="B4" t="n">
-        <v>98262</v>
+        <v>98266</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>125941601</v>
       </c>
       <c r="B5" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 27397-2025 artfynd.xlsx
+++ b/artfynd/A 27397-2025 artfynd.xlsx
@@ -972,7 +972,7 @@
         <v>125940765</v>
       </c>
       <c r="B4" t="n">
-        <v>98266</v>
+        <v>98269</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27397-2025 artfynd.xlsx
+++ b/artfynd/A 27397-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125940706</v>
       </c>
       <c r="B2" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>125941678</v>
       </c>
       <c r="B3" t="n">
-        <v>57653</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -972,7 +972,7 @@
         <v>125940765</v>
       </c>
       <c r="B4" t="n">
-        <v>98269</v>
+        <v>98278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1094,7 +1094,7 @@
         <v>125941601</v>
       </c>
       <c r="B5" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
